--- a/artfynd/A 52285-2025 artfynd.xlsx
+++ b/artfynd/A 52285-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688345</v>
       </c>
       <c r="B2" t="n">
-        <v>78829</v>
+        <v>78833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688346</v>
       </c>
       <c r="B3" t="n">
-        <v>78828</v>
+        <v>78832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52285-2025 artfynd.xlsx
+++ b/artfynd/A 52285-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688345</v>
       </c>
       <c r="B2" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688346</v>
       </c>
       <c r="B3" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52285-2025 artfynd.xlsx
+++ b/artfynd/A 52285-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688345</v>
       </c>
       <c r="B2" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688346</v>
       </c>
       <c r="B3" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52285-2025 artfynd.xlsx
+++ b/artfynd/A 52285-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688345</v>
       </c>
       <c r="B2" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688346</v>
       </c>
       <c r="B3" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52285-2025 artfynd.xlsx
+++ b/artfynd/A 52285-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688345</v>
       </c>
       <c r="B2" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688346</v>
       </c>
       <c r="B3" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52285-2025 artfynd.xlsx
+++ b/artfynd/A 52285-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688345</v>
       </c>
       <c r="B2" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688346</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52285-2025 artfynd.xlsx
+++ b/artfynd/A 52285-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688345</v>
       </c>
       <c r="B2" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688346</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
